--- a/output/full_scan/batch_seq1_2026-07-03.xlsx
+++ b/output/full_scan/batch_seq1_2026-07-03.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O131"/>
+  <dimension ref="A1:O133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1310</v>
+        <v>1303</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>812.579212631228</v>
+        <v>818.0056461115212</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11.4</v>
+        <v>197</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>71.94670716257981</v>
+        <v>84.55455661784173</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35.04992278784491</v>
+        <v>40.53143561654046</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.857921263122795</v>
+        <v>0.5186965431107601</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.183988999954443</v>
+        <v>5.756160054049914</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1440</v>
+        <v>1310</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>810.1618930552069</v>
+        <v>812.579212631228</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>14.45</v>
+        <v>11.4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.38297397564926</v>
+        <v>71.94670716257981</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>21.95148382975626</v>
+        <v>35.04992278784491</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.749796266857048</v>
+        <v>2.857921263122795</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0519872335084015</v>
+        <v>0.183988999954443</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1409</v>
+        <v>1440</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>810.0745133727453</v>
+        <v>810.1618930552069</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>31</v>
+        <v>14.45</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>68.77009243949752</v>
+        <v>65.38297397564926</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.71723131082455</v>
+        <v>21.95148382975626</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.655388397604696</v>
+        <v>1.749796266857048</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.058555485167179</v>
+        <v>0.0519872335084015</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1465</v>
+        <v>1409</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>809.9750013005497</v>
+        <v>810.0745133727453</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12.95</v>
+        <v>31</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>67.98813129418269</v>
+        <v>68.77009243949752</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16.55664876970444</v>
+        <v>24.71723131082455</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.863020569356908</v>
+        <v>2.655388397604696</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0270860792018395</v>
+        <v>-0.058555485167179</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1315</v>
+        <v>1465</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>804.0241678587208</v>
+        <v>809.9750013005497</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>64</v>
+        <v>12.95</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>70.8408804194236</v>
+        <v>67.98813129418269</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>13.11427050970934</v>
+        <v>16.55664876970444</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.721108860039289</v>
+        <v>1.863020569356908</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.177971845891771</v>
+        <v>0.0270860792018395</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1459</v>
+        <v>1315</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>801.6517035743033</v>
+        <v>804.0241678587208</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.52154575706472</v>
+        <v>70.8408804194236</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>16.35435343581837</v>
+        <v>13.11427050970934</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.567875801847613</v>
+        <v>1.721108860039289</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0190588719309453</v>
+        <v>0.177971845891771</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>784.9094659672328</v>
+        <v>801.6517035743033</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>14.3</v>
+        <v>12</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>74.79408303414219</v>
+        <v>60.52154575706472</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>34.6208568627485</v>
+        <v>16.35435343581837</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4.090946596723282</v>
+        <v>3.567875801847613</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2255796773391143</v>
+        <v>0.0190588719309453</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1227</v>
+        <v>1313</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>782.7535444467048</v>
+        <v>784.9094659672328</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>30</v>
+        <v>14.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>66.24798966783982</v>
+        <v>74.79408303414219</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21.79393608127383</v>
+        <v>34.6208568627485</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.472731396173413</v>
+        <v>4.090946596723282</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.08183504228591509</v>
+        <v>0.2255796773391143</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1437</v>
+        <v>1227</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>778.961631276163</v>
+        <v>782.7535444467048</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>31.1</v>
+        <v>30</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>79.39744770195036</v>
+        <v>66.24798966783982</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.91314686304433</v>
+        <v>21.79393608127383</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.930862637272882</v>
+        <v>1.472731396173413</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1148403148498922</v>
+        <v>0.08183504228591509</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1326</v>
+        <v>1437</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>778.289831525774</v>
+        <v>778.961631276163</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>68</v>
+        <v>31.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>72.10455371449464</v>
+        <v>79.39744770195036</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>25.31026722519016</v>
+        <v>27.91314686304433</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.428983152577408</v>
+        <v>1.930862637272882</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.063445401668322</v>
+        <v>0.1148403148498922</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1452</v>
+        <v>1326</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>769.1410953642263</v>
+        <v>778.289831525774</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11.95</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>74.77805027494989</v>
+        <v>72.10455371449464</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>17.27030090284766</v>
+        <v>25.31026722519016</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4.143707904974146</v>
+        <v>2.428983152577408</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0750914045796654</v>
+        <v>1.063445401668322</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1301</v>
+        <v>1452</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>765.1031128109336</v>
+        <v>769.1410953642263</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>62.1</v>
+        <v>11.95</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>69.04524659815442</v>
+        <v>74.77805027494989</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>27.52345910691155</v>
+        <v>17.27030090284766</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3.110311281093355</v>
+        <v>4.143707904974146</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.128624060505466</v>
+        <v>0.0750914045796654</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1531</v>
+        <v>1301</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>762.2522321922924</v>
+        <v>765.1031128109336</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>13.1</v>
+        <v>62.1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>62.70192771825521</v>
+        <v>69.04524659815442</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14.55264226764871</v>
+        <v>27.52345910691155</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.438147327267658</v>
+        <v>3.110311281093355</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.007343395500027</v>
+        <v>1.128624060505466</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1305</v>
+        <v>1531</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>754</v>
+        <v>762.2522321922924</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>14.85</v>
+        <v>13.1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>67.77062131587375</v>
+        <v>62.70192771825521</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11.76616717364167</v>
+        <v>14.55264226764871</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5.882970271713754</v>
+        <v>1.438147327267658</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1788811812875741</v>
+        <v>0.007343395500027</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1536</v>
+        <v>1305</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>746.3842063679871</v>
+        <v>754</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>52.2</v>
+        <v>14.85</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>58.89303509167977</v>
+        <v>67.77062131587375</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12.37286439046641</v>
+        <v>11.76616717364167</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3.309103093133573</v>
+        <v>5.882970271713754</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.33670557320606</v>
+        <v>0.1788811812875741</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1515</v>
+        <v>1536</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>724.2992380040318</v>
+        <v>746.3842063679871</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>42</v>
+        <v>52.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>89.87717995651204</v>
+        <v>58.89303509167977</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>48.24954121816895</v>
+        <v>12.37286439046641</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.529923800403179</v>
+        <v>3.309103093133573</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.537521931957055</v>
+        <v>0.33670557320606</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1304</v>
+        <v>1515</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>714.988916237103</v>
+        <v>724.2992380040318</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>70.05649500202152</v>
+        <v>89.87717995651204</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15.36913928015224</v>
+        <v>48.24954121816895</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>4.098891623710302</v>
+        <v>3.529923800403179</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.2071366968391176</v>
+        <v>1.537521931957055</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1323</v>
+        <v>1304</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>706.8170211954022</v>
+        <v>714.988916237103</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>20.45</v>
+        <v>15.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>59.91286779218414</v>
+        <v>70.05649500202152</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.9807502302771</v>
+        <v>15.36913928015224</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.574770754709517</v>
+        <v>4.098891623710302</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0502869137141863</v>
+        <v>0.2071366968391176</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1102</v>
+        <v>1323</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>699.782393781435</v>
+        <v>706.8170211954022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>36.45</v>
+        <v>20.45</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>62.05974250272509</v>
+        <v>59.91286779218414</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.05355757486864</v>
+        <v>15.9807502302771</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8489779503109035</v>
+        <v>1.574770754709517</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0608547035172015</v>
+        <v>0.0502869137141863</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1308</v>
+        <v>1102</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>693.8851896299569</v>
+        <v>699.782393781435</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>15.85</v>
+        <v>36.45</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>70.66635558483182</v>
+        <v>62.05974250272509</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>15.17069310362512</v>
+        <v>20.05355757486864</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4.988518962995694</v>
+        <v>0.8489779503109035</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1816980175100932</v>
+        <v>0.0608547035172015</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1229</v>
+        <v>1308</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>690.7686671335566</v>
+        <v>693.8851896299569</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>43.75</v>
+        <v>15.85</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>63.5603412722295</v>
+        <v>70.66635558483182</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>24.41777866052282</v>
+        <v>15.17069310362512</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.425601641052894</v>
+        <v>4.988518962995694</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.154460490486622</v>
+        <v>0.1816980175100932</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1460</v>
+        <v>1229</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>689</v>
+        <v>690.7686671335566</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>8.58</v>
+        <v>43.75</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>82.16351433180142</v>
+        <v>63.5603412722295</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.42390870553749</v>
+        <v>24.41777866052282</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>7.610113772604651</v>
+        <v>1.425601641052894</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1186032456848046</v>
+        <v>0.154460490486622</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1110</v>
+        <v>1460</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>679.4414840872721</v>
+        <v>689</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>15.95</v>
+        <v>8.58</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>61.20985389323877</v>
+        <v>82.16351433180142</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>31.38792557758373</v>
+        <v>20.42390870553749</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.626031146911898</v>
+        <v>7.610113772604651</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0141467840347757</v>
+        <v>0.1186032456848046</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1447</v>
+        <v>1110</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>679</v>
+        <v>679.4414840872721</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>9.99</v>
+        <v>15.95</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>88.09106108016609</v>
+        <v>61.20985389323877</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>37.64929185531273</v>
+        <v>31.38792557758373</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>6.033825465753735</v>
+        <v>1.626031146911898</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3555487921494022</v>
+        <v>0.0141467840347757</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1413</v>
+        <v>1447</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>676.3681713152776</v>
+        <v>679</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>9.56</v>
+        <v>9.99</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>55.19636091880044</v>
+        <v>88.09106108016609</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.5113400638477</v>
+        <v>37.64929185531273</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>4.16735672405273</v>
+        <v>6.033825465753735</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.002371654170787</v>
+        <v>0.3555487921494022</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1210</v>
+        <v>1413</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>676.31118654235</v>
+        <v>676.3681713152776</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>58</v>
+        <v>9.56</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>74.88006696368018</v>
+        <v>55.19636091880044</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>36.85508628268794</v>
+        <v>17.5113400638477</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.180448752406251</v>
+        <v>4.16735672405273</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.2244150101472877</v>
+        <v>0.002371654170787</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1307</v>
+        <v>1210</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>675.3778851494823</v>
+        <v>676.31118654235</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>35.8</v>
+        <v>58</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.90794287220261</v>
+        <v>74.88006696368018</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.52324399460369</v>
+        <v>36.85508628268794</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.822085069758944</v>
+        <v>1.180448752406251</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.19364791051532</v>
+        <v>0.2244150101472877</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1324</v>
+        <v>1307</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>670.9358560659806</v>
+        <v>675.3778851494823</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>10.85</v>
+        <v>35.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>64.09774196069682</v>
+        <v>58.90794287220261</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19.71937224701476</v>
+        <v>20.52324399460369</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>3.809578391111709</v>
+        <v>1.822085069758944</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0353192016898322</v>
+        <v>-0.19364791051532</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1445</v>
+        <v>1324</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>665.6768473157854</v>
+        <v>670.9358560659806</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>12.6</v>
+        <v>10.85</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>66.16330882618621</v>
+        <v>64.09774196069682</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27.73839763645586</v>
+        <v>19.71937224701476</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4.167684731578538</v>
+        <v>3.809578391111709</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.208307478108823</v>
+        <v>0.0353192016898322</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1217</v>
+        <v>1445</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>658.1177043965697</v>
+        <v>665.6768473157854</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>10.15</v>
+        <v>12.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>69.66019062143171</v>
+        <v>66.16330882618621</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>17.52046908312788</v>
+        <v>27.73839763645586</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.070507195446158</v>
+        <v>4.167684731578538</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0218698438198633</v>
+        <v>0.208307478108823</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>650.8580233368067</v>
+        <v>658.1177043965697</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>76.3</v>
+        <v>10.15</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>59.33466691788323</v>
+        <v>69.66019062143171</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>24.79898755704686</v>
+        <v>17.52046908312788</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.146674731542372</v>
+        <v>2.070507195446158</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0506814538088563</v>
+        <v>0.0218698438198633</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1467</v>
+        <v>1216</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>633.875724718196</v>
+        <v>650.8580233368067</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>9.710000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>84.94328408513121</v>
+        <v>59.33466691788323</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>27.03210896739424</v>
+        <v>24.79898755704686</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.987572471819604</v>
+        <v>1.146674731542372</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.2172114271544996</v>
+        <v>-0.0506814538088563</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>628.6402453445288</v>
+        <v>633.875724718196</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>18.4</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>78.92146653642271</v>
+        <v>84.94328408513121</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.06681698678954</v>
+        <v>27.03210896739424</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.964024534452883</v>
+        <v>2.987572471819604</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4727999576704831</v>
+        <v>0.2172114271544996</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>628.6314917653106</v>
+        <v>628.6402453445288</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11</v>
+        <v>18.4</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>71.04774872894296</v>
+        <v>78.92146653642271</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20.59204657904167</v>
+        <v>21.06681698678954</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.963149176531056</v>
+        <v>2.964024534452883</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.07005940055773779</v>
+        <v>0.4727999576704831</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2912,21 +2912,21 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1441</v>
+        <v>1464</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>626.4249981128855</v>
+        <v>628.6314917653106</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>9.69</v>
+        <v>11</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>62.97764214221043</v>
+        <v>71.04774872894296</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.44983176455205</v>
+        <v>20.59204657904167</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.635290747230271</v>
+        <v>2.963149176531056</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.07168223090232639</v>
+        <v>0.07005940055773779</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1512</v>
+        <v>1441</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>618.8816768215663</v>
+        <v>626.4249981128855</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>7.15</v>
+        <v>9.69</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>57.20595580783726</v>
+        <v>62.97764214221043</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>9.970365435076005</v>
+        <v>22.44983176455205</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.868286410330453</v>
+        <v>1.635290747230271</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.018032667105832</v>
+        <v>0.07168223090232639</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1309</v>
+        <v>1512</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>608.4459189781314</v>
+        <v>618.8816768215663</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>16.7</v>
+        <v>7.15</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>59.79934382753368</v>
+        <v>57.20595580783726</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.08057447981335</v>
+        <v>9.970365435076005</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4.763674679022635</v>
+        <v>1.868286410330453</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.2329371033116043</v>
+        <v>0.018032667105832</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1560</v>
+        <v>1309</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>601.6072630869354</v>
+        <v>608.4459189781314</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>756</v>
+        <v>16.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>59.89884617108572</v>
+        <v>59.79934382753368</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24.0475579482023</v>
+        <v>13.08057447981335</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4702055930996314</v>
+        <v>4.763674679022635</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>3.81738904044688</v>
+        <v>0.2329371033116043</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1442</v>
+        <v>1560</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>600.90625020248</v>
+        <v>601.6072630869354</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>28.5</v>
+        <v>756</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>61.54252090495857</v>
+        <v>59.89884617108572</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>18.13121471155267</v>
+        <v>24.0475579482023</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.49422232019621</v>
+        <v>0.4702055930996314</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0633012220547042</v>
+        <v>3.81738904044688</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1232</v>
+        <v>1442</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>596.8046707457489</v>
+        <v>600.90625020248</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>146.5</v>
+        <v>28.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>56.72052585480495</v>
+        <v>61.54252090495857</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>34.07928382235796</v>
+        <v>18.13121471155267</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3.08327007153129</v>
+        <v>1.49422232019621</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.232179702293352</v>
+        <v>0.0633012220547042</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1444</v>
+        <v>1232</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>586.6384176162079</v>
+        <v>596.8046707457489</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>146.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>85.20962496395914</v>
+        <v>56.72052585480495</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>42.56287027936579</v>
+        <v>34.07928382235796</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2.763841761620787</v>
+        <v>3.08327007153129</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.3013785665996157</v>
+        <v>0.232179702293352</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1451</v>
+        <v>1444</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>584.1789661838925</v>
+        <v>586.6384176162079</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>17.4</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>65.31986769075633</v>
+        <v>85.20962496395914</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.96338633875453</v>
+        <v>42.56287027936579</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.838785059885466</v>
+        <v>2.763841761620787</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.058902866113238</v>
+        <v>0.3013785665996157</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1419</v>
+        <v>1451</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>571.2498063777696</v>
+        <v>584.1789661838925</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>66.2</v>
+        <v>17.4</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>53.8717458132345</v>
+        <v>65.31986769075633</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.28813414260482</v>
+        <v>16.96338633875453</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.536554644323752</v>
+        <v>1.838785059885466</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.1740414696835659</v>
+        <v>0.058902866113238</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1402</v>
+        <v>1419</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>571.0211565546358</v>
+        <v>571.2498063777696</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>29.1</v>
+        <v>66.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>61.37708198274788</v>
+        <v>53.8717458132345</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.67200549742605</v>
+        <v>14.28813414260482</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7517456184858882</v>
+        <v>1.536554644323752</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0125813999621839</v>
+        <v>-0.1740414696835659</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1342</v>
+        <v>1402</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>570.9649981278958</v>
+        <v>571.0211565546358</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>115.5</v>
+        <v>29.1</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>61.65775029394126</v>
+        <v>61.37708198274788</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>37.75057696608277</v>
+        <v>18.67200549742605</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.484144464759514</v>
+        <v>0.7517456184858882</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.7887572148519197</v>
+        <v>-0.0125813999621839</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1321</v>
+        <v>1342</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>547.349241137969</v>
+        <v>570.9649981278958</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>31.9</v>
+        <v>115.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>61.61249198231518</v>
+        <v>61.65775029394126</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>30.92540983759661</v>
+        <v>37.75057696608277</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6821205126328416</v>
+        <v>0.484144464759514</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0459341197280617</v>
+        <v>-0.7887572148519197</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1423</v>
+        <v>1321</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>545.4228932401827</v>
+        <v>547.349241137969</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>36.95</v>
+        <v>31.9</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>29.22359857056203</v>
+        <v>61.61249198231518</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>35.90023013383686</v>
+        <v>30.92540983759661</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.0409158868135302</v>
+        <v>0.6821205126328416</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.5043443414491044</v>
+        <v>0.0459341197280617</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1414</v>
+        <v>1423</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>543.8781810929316</v>
+        <v>545.4228932401827</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>19.45</v>
+        <v>36.95</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>78.08192059903648</v>
+        <v>29.22359857056203</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>26.90426838205534</v>
+        <v>35.90023013383686</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.710270534949198</v>
+        <v>0.0409158868135302</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.2224242990294189</v>
+        <v>-0.5043443414491044</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1558</v>
+        <v>1414</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>542.8127768020843</v>
+        <v>543.8781810929316</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>19.45</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>59.43282596631465</v>
+        <v>78.08192059903648</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>10.27773710304792</v>
+        <v>26.90426838205534</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.758663539480723</v>
+        <v>1.710270534949198</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.08971948525012879</v>
+        <v>0.2224242990294189</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1513</v>
+        <v>1558</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>541.9796820221126</v>
+        <v>542.8127768020843</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>176.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>55.83425087214585</v>
+        <v>59.43282596631465</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.22419906216046</v>
+        <v>10.27773710304792</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2316844389941585</v>
+        <v>1.758663539480723</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.6753706588524349</v>
+        <v>0.08971948525012879</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1503</v>
+        <v>1513</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>534.2670515544619</v>
+        <v>541.9796820221126</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>238</v>
+        <v>176.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>55.90084223077148</v>
+        <v>55.83425087214585</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.58437774194034</v>
+        <v>18.22419906216046</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.237635452731361</v>
+        <v>0.2316844389941585</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.170353030690154</v>
+        <v>-0.6753706588524349</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1103</v>
+        <v>1435</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>532.3803372516991</v>
+        <v>536.301194794117</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>13.65</v>
+        <v>29.75</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>56.29722024944452</v>
+        <v>62.50482535133683</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>11.58991015990721</v>
+        <v>15.47576057778286</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.721049977228546</v>
+        <v>1.862686930461108</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.0195097090229428</v>
+        <v>2.183995480929074</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1463</v>
+        <v>1503</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>522.4745708617797</v>
+        <v>534.2670515544619</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>17.8</v>
+        <v>238</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>55.83029878915777</v>
+        <v>55.90084223077148</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>24.6321963356313</v>
+        <v>19.58437774194034</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.055418045076993</v>
+        <v>0.237635452731361</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0401284232939899</v>
+        <v>-1.170353030690154</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1532</v>
+        <v>1103</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>515.4099237694694</v>
+        <v>532.3803372516991</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>23.4</v>
+        <v>13.65</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>61.5724839870513</v>
+        <v>56.29722024944452</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>30.05256636134736</v>
+        <v>11.58991015990721</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.8004511867370777</v>
+        <v>1.721049977228546</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.085955301714764</v>
+        <v>-0.0195097090229428</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>514.5988329364596</v>
+        <v>522.4745708617797</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>12.25</v>
+        <v>17.8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>61.17193950033702</v>
+        <v>55.83029878915777</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>12.40361384592949</v>
+        <v>24.6321963356313</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7770564484205527</v>
+        <v>2.055418045076993</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0396656796354326</v>
+        <v>0.0401284232939899</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1236</v>
+        <v>1532</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>483.4999880767747</v>
+        <v>515.4099237694694</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>25.6</v>
+        <v>23.4</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.37877822583685</v>
+        <v>61.5724839870513</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11.18640952356062</v>
+        <v>30.05256636134736</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.066511089652213</v>
+        <v>0.8004511867370777</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0304516586918953</v>
+        <v>-0.085955301714764</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1256</v>
+        <v>1468</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>483.1510814908942</v>
+        <v>514.5988329364596</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>193</v>
+        <v>12.25</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>62.35826056645081</v>
+        <v>61.17193950033702</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.48755554979213</v>
+        <v>12.40361384592949</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.180544275475259</v>
+        <v>0.7770564484205527</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.8127181392737322</v>
+        <v>0.0396656796354326</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1475</v>
+        <v>1236</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>476.7700555052008</v>
+        <v>483.4999880767747</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>27.45</v>
+        <v>25.6</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>58.06570401053438</v>
+        <v>53.37877822583685</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.26870247553311</v>
+        <v>11.18640952356062</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3715936172417366</v>
+        <v>2.066511089652213</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0441113611351373</v>
+        <v>-0.0304516586918953</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1203</v>
+        <v>1256</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>475.0767248775614</v>
+        <v>483.1510814908942</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>43.35</v>
+        <v>193</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.47942573100754</v>
+        <v>62.35826056645081</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>12.31600420455999</v>
+        <v>15.48755554979213</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8090565046921037</v>
+        <v>1.180544275475259</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0166510070537447</v>
+        <v>0.8127181392737322</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1108</v>
+        <v>1475</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>467.1087325135224</v>
+        <v>476.7700555052008</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>13.9</v>
+        <v>27.45</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.75127819116111</v>
+        <v>58.06570401053438</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>22.72211521213144</v>
+        <v>18.26870247553311</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.576582169405905</v>
+        <v>0.3715936172417366</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0183588909304685</v>
+        <v>0.0441113611351373</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1472</v>
+        <v>1203</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>460.1739912170954</v>
+        <v>475.0767248775614</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>87.59999999999999</v>
+        <v>43.35</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.85062100088307</v>
+        <v>53.47942573100754</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10.35201081972429</v>
+        <v>12.31600420455999</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.1170003589886617</v>
+        <v>0.8090565046921037</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.3311933671207994</v>
+        <v>0.0166510070537447</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1533</v>
+        <v>1108</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>459.7386492223204</v>
+        <v>467.1087325135224</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>37.5</v>
+        <v>13.9</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>53.7105810874364</v>
+        <v>52.75127819116111</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>29.57186103945797</v>
+        <v>22.72211521213144</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6313695501142084</v>
+        <v>2.576582169405905</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.2483820750262792</v>
+        <v>0.0183588909304685</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1568</v>
+        <v>1472</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>459.3512774951975</v>
+        <v>460.1739912170954</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>39.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.04303277901803</v>
+        <v>47.85062100088307</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>31.42137834799797</v>
+        <v>10.35201081972429</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.295015003932434</v>
+        <v>0.1170003589886617</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.9049737369255776</v>
+        <v>-0.3311933671207994</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1446</v>
+        <v>1533</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>459.1296221411817</v>
+        <v>459.7386492223204</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>17.7</v>
+        <v>37.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>73.17999137965292</v>
+        <v>53.7105810874364</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>27.48243047366563</v>
+        <v>29.57186103945797</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.59118831364585</v>
+        <v>0.6313695501142084</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0933741580759561</v>
+        <v>-0.2483820750262792</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1220</v>
+        <v>1568</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>458.1153507149025</v>
+        <v>459.3512774951975</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>11.85</v>
+        <v>39.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>56.18583569154647</v>
+        <v>51.04303277901803</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26.92316422074494</v>
+        <v>31.42137834799797</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7703313198745718</v>
+        <v>1.295015003932434</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0370649841837212</v>
+        <v>-0.9049737369255776</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1540</v>
+        <v>1446</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>446.0016813067942</v>
+        <v>459.1296221411817</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>22.8</v>
+        <v>17.7</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>62.24729141523351</v>
+        <v>73.17999137965292</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.02410858235783</v>
+        <v>27.48243047366563</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.434769694839104</v>
+        <v>2.59118831364585</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.077962054117619</v>
+        <v>0.0933741580759561</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1471</v>
+        <v>1220</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>426.5961117333616</v>
+        <v>458.1153507149025</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>11.1</v>
+        <v>11.85</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.7840927508714</v>
+        <v>56.18583569154647</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>10.93649387979997</v>
+        <v>26.92316422074494</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.054817680647735</v>
+        <v>0.7703313198745718</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.001136172787854</v>
+        <v>0.0370649841837212</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1340</v>
+        <v>1540</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>422.1832581828861</v>
+        <v>446.0016813067942</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>5.84</v>
+        <v>22.8</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>60.69470702423639</v>
+        <v>62.24729141523351</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.26013124493053</v>
+        <v>16.02410858235783</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.078391938527436</v>
+        <v>1.434769694839104</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0085807308363297</v>
+        <v>0.077962054117619</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, williams_r_recovery</t>
+          <t>rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1504</v>
+        <v>1471</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>421.9377690940692</v>
+        <v>426.5961117333616</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>70</v>
+        <v>11.1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>48.02569351269928</v>
+        <v>51.7840927508714</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.14472226618744</v>
+        <v>10.93649387979997</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3115639656977321</v>
+        <v>1.054817680647735</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.3406136173448021</v>
+        <v>0.001136172787854</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1514</v>
+        <v>1340</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>416.8493358676108</v>
+        <v>422.1832581828861</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>123</v>
+        <v>5.84</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>50.17448784071456</v>
+        <v>60.69470702423639</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.04319713802205</v>
+        <v>16.26013124493053</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.676453135485969</v>
+        <v>2.078391938527436</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.3220448371453556</v>
+        <v>0.0085807308363297</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1457</v>
+        <v>1504</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>400.9722466443673</v>
+        <v>421.9377690940692</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>14.7</v>
+        <v>70</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>58.18227872448652</v>
+        <v>48.02569351269928</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.8804808359129</v>
+        <v>13.14472226618744</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.3915046100318</v>
+        <v>0.3115639656977321</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0225636318207232</v>
+        <v>-0.3406136173448021</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1477</v>
+        <v>1514</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>399.0505715534712</v>
+        <v>416.8493358676108</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>228.5</v>
+        <v>123</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>57.35889147490222</v>
+        <v>50.17448784071456</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>18.88245013975542</v>
+        <v>17.04319713802205</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8831938122357599</v>
+        <v>0.676453135485969</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.8903527753886736</v>
+        <v>-0.3220448371453556</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1231</v>
+        <v>1457</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>398.7996989420072</v>
+        <v>400.9722466443673</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>88.5</v>
+        <v>14.7</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>55.49048276846761</v>
+        <v>58.18227872448652</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.20805899888013</v>
+        <v>13.8804808359129</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.935937007001978</v>
+        <v>1.3915046100318</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0788290814500115</v>
+        <v>0.0225636318207232</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1410</v>
+        <v>1477</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>385.4396542860904</v>
+        <v>399.0505715534712</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>25.65</v>
+        <v>228.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>50.24140025763673</v>
+        <v>57.35889147490222</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.2177666119582</v>
+        <v>18.88245013975542</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>3.482628769372403</v>
+        <v>0.8831938122357599</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.2431989959608198</v>
+        <v>0.8903527753886736</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1215</v>
+        <v>1231</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>378.2490833368335</v>
+        <v>398.7996989420072</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>112.5</v>
+        <v>88.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>35.2418702503049</v>
+        <v>55.49048276846761</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46.17439576881266</v>
+        <v>16.20805899888013</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4767941232980652</v>
+        <v>0.935937007001978</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.4573724226872047</v>
+        <v>0.0788290814500115</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1225</v>
+        <v>1410</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>376.9239870173078</v>
+        <v>385.4396542860904</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>28.65</v>
+        <v>25.65</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>39.44866100099541</v>
+        <v>50.24140025763673</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.87423224171405</v>
+        <v>17.2177666119582</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7254098688560282</v>
+        <v>3.482628769372403</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.2178238777821957</v>
+        <v>0.2431989959608198</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1417</v>
+        <v>1215</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>372.1219894335868</v>
+        <v>378.2490833368335</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>112.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>70.28931273968932</v>
+        <v>35.2418702503049</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>19.20631087692217</v>
+        <v>46.17439576881266</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.721890753500603</v>
+        <v>0.4767941232980652</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0792812009652723</v>
+        <v>0.4573724226872047</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1316</v>
+        <v>1225</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>368.5108154147575</v>
+        <v>376.9239870173078</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>10.95</v>
+        <v>28.65</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>56.14982302471396</v>
+        <v>39.44866100099541</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.05685669474149</v>
+        <v>16.87423224171405</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.315892290552356</v>
+        <v>0.7254098688560282</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0357487448429587</v>
+        <v>-0.2178238777821957</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1537</v>
+        <v>1417</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>361.8304667680621</v>
+        <v>372.1219894335868</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>126.5</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.94851900858357</v>
+        <v>70.28931273968932</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.50548250911368</v>
+        <v>19.20631087692217</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4589657676196894</v>
+        <v>2.721890753500603</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1391990653647605</v>
+        <v>0.0792812009652723</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1526</v>
+        <v>1316</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>360.1037597867586</v>
+        <v>368.5108154147575</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>14.95</v>
+        <v>10.95</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>56.87158735025557</v>
+        <v>56.14982302471396</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>22.01525153182272</v>
+        <v>14.05685669474149</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2.143682819416516</v>
+        <v>1.315892290552356</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.07101483741797281</v>
+        <v>0.0357487448429587</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1521</v>
+        <v>1537</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>355.1739638771749</v>
+        <v>361.8304667680621</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>26.25</v>
+        <v>126.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.14611249077053</v>
+        <v>52.94851900858357</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>14.28488609420241</v>
+        <v>19.50548250911368</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4412068356087198</v>
+        <v>0.4589657676196894</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1136038772598811</v>
+        <v>-0.1391990653647605</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1470</v>
+        <v>1526</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>346.0536379353524</v>
+        <v>360.1037597867586</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>21</v>
+        <v>14.95</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>51.48835760634071</v>
+        <v>56.87158735025557</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>8.921137294460429</v>
+        <v>22.01525153182272</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.1855350996742972</v>
+        <v>2.143682819416516</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.8095799727492083</v>
+        <v>0.07101483741797281</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1432</v>
+        <v>1521</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>342.929553951324</v>
+        <v>355.1739638771749</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>15.2</v>
+        <v>26.25</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>29.87257787737066</v>
+        <v>52.14611249077053</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>32.68711331203323</v>
+        <v>14.28488609420241</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5596373032194462</v>
+        <v>0.4412068356087198</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1886003026536934</v>
+        <v>-0.1136038772598811</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1443</v>
+        <v>1470</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>309.9170051760354</v>
+        <v>346.0536379353524</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>26.35</v>
+        <v>21</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.78760705779384</v>
+        <v>51.48835760634071</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.09212664621731</v>
+        <v>8.921137294460429</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.1870275565971588</v>
+        <v>0.1855350996742972</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1789801296629976</v>
+        <v>0.8095799727492083</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1582</v>
+        <v>1432</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>308.2715025176302</v>
+        <v>342.929553951324</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>82.7</v>
+        <v>15.2</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>35.83055390482221</v>
+        <v>29.87257787737066</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>21.49284905675819</v>
+        <v>32.68711331203323</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3597138354673648</v>
+        <v>0.5596373032194462</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.8273357971514965</v>
+        <v>-0.1886003026536934</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1436</v>
+        <v>1443</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>306.8181182405764</v>
+        <v>309.9170051760354</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>45.6</v>
+        <v>26.35</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.08498396487632</v>
+        <v>49.78760705779384</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.73845979843538</v>
+        <v>16.09212664621731</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8341892783420224</v>
+        <v>0.1870275565971588</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0728496477846332</v>
+        <v>-0.1789801296629976</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1416</v>
+        <v>1582</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>298.2988398900664</v>
+        <v>308.2715025176302</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>11.2</v>
+        <v>82.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>54.50609397589507</v>
+        <v>35.83055390482221</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>22.44344411103675</v>
+        <v>21.49284905675819</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.101383938257255</v>
+        <v>0.3597138354673648</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0239654624634853</v>
+        <v>-0.8273357971514965</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1213</v>
+        <v>1436</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>297.5275736512192</v>
+        <v>306.8181182405764</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>7.9</v>
+        <v>45.6</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>50.31863692167251</v>
+        <v>48.08498396487632</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>7.24860724275231</v>
+        <v>17.73845979843538</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>3.349133997963344</v>
+        <v>0.8341892783420224</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0845759133160759</v>
+        <v>0.0728496477846332</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1219</v>
+        <v>1416</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>287.5707442534592</v>
+        <v>298.2988398900664</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>12.4</v>
+        <v>11.2</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>40.46301254441288</v>
+        <v>54.50609397589507</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>28.3039731257897</v>
+        <v>22.44344411103675</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.695369767977084</v>
+        <v>1.101383938257255</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0146151718034143</v>
+        <v>0.0239654624634853</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1524</v>
+        <v>1213</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>285.4605394574159</v>
+        <v>297.5275736512192</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>29.65</v>
+        <v>7.9</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.94405718797278</v>
+        <v>50.31863692167251</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.53232495534265</v>
+        <v>7.24860724275231</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.028443116519252</v>
+        <v>3.349133997963344</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0558054520216996</v>
+        <v>0.0845759133160759</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1339</v>
+        <v>1219</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>284.2026830665107</v>
+        <v>287.5707442534592</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>44.75</v>
+        <v>12.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>58.68933751134897</v>
+        <v>40.46301254441288</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.16871491933266</v>
+        <v>28.3039731257897</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6963972702670037</v>
+        <v>2.695369767977084</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0453223155508278</v>
+        <v>0.0146151718034143</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1233</v>
+        <v>1524</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>283.7625960028538</v>
+        <v>285.4605394574159</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>28.2</v>
+        <v>29.65</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.77010044076796</v>
+        <v>49.94405718797278</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11.25354925607232</v>
+        <v>14.53232495534265</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.654474278922943</v>
+        <v>1.028443116519252</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.07119435369226861</v>
+        <v>-0.0558054520216996</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1438</v>
+        <v>1339</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>274.8624482094697</v>
+        <v>284.2026830665107</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>22.5</v>
+        <v>44.75</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>51.56479337988547</v>
+        <v>58.68933751134897</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>21.18304942019164</v>
+        <v>17.16871491933266</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.1877273223535865</v>
+        <v>0.6963972702670037</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0746417811725759</v>
+        <v>-0.0453223155508278</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1539</v>
+        <v>1233</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>271.9873795824526</v>
+        <v>283.7625960028538</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>16.05</v>
+        <v>28.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>56.09864407502307</v>
+        <v>50.77010044076796</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.4755186734851</v>
+        <v>11.25354925607232</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.07571520808781</v>
+        <v>1.654474278922943</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0389340863898131</v>
+        <v>0.07119435369226861</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1528</v>
+        <v>1438</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>270.5083971234804</v>
+        <v>274.8624482094697</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>24.2</v>
+        <v>22.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.37718926540751</v>
+        <v>51.56479337988547</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.365872982676091</v>
+        <v>21.18304942019164</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4754993359110761</v>
+        <v>0.1877273223535865</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0972586080827285</v>
+        <v>0.0746417811725759</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1319</v>
+        <v>1539</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>267.6284617909479</v>
+        <v>271.9873795824526</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>77.2</v>
+        <v>16.05</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>38.55357057081569</v>
+        <v>56.09864407502307</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>31.48833309695618</v>
+        <v>13.4755186734851</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.311653923132687</v>
+        <v>1.07571520808781</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-2.225271154611944</v>
+        <v>0.0389340863898131</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1454</v>
+        <v>1528</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>262.7060160260297</v>
+        <v>270.5083971234804</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>13.05</v>
+        <v>24.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>54.18528417799328</v>
+        <v>44.37718926540751</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15.39939537862522</v>
+        <v>9.365872982676091</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.243349979941853</v>
+        <v>0.4754993359110761</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0230902217707354</v>
+        <v>-0.0972586080827285</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1453</v>
+        <v>1319</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>261.7521030911496</v>
+        <v>267.6284617909479</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>11.55</v>
+        <v>77.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>52.66447748784137</v>
+        <v>38.55357057081569</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>22.99849884995478</v>
+        <v>31.48833309695618</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4772903593278928</v>
+        <v>0.311653923132687</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0188233760976718</v>
+        <v>-2.225271154611944</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1341</v>
+        <v>1454</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>260.3773446632664</v>
+        <v>262.7060160260297</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>58.5</v>
+        <v>13.05</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.95947555975402</v>
+        <v>54.18528417799328</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>23.63908444500468</v>
+        <v>15.39939537862522</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4368356149415419</v>
+        <v>1.243349979941853</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-2.365389142328266</v>
+        <v>0.0230902217707354</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1538</v>
+        <v>1453</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>240.9769100970456</v>
+        <v>261.7521030911496</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>0</v>
+        <v>11.55</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.26849370565207</v>
+        <v>52.66447748784137</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>7.914387308078068</v>
+        <v>22.99849884995478</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.0525884112510252</v>
+        <v>0.4772903593278928</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-1.124186720707706</v>
+        <v>-0.0188233760976718</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1516</v>
+        <v>1341</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>234.6484352184154</v>
+        <v>260.3773446632664</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>18.8</v>
+        <v>58.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>34.5166154466913</v>
+        <v>50.95947555975402</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>31.548461037437</v>
+        <v>23.63908444500468</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.8302572936319143</v>
+        <v>0.4368356149415419</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1803676867645468</v>
+        <v>-2.365389142328266</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1519</v>
+        <v>1538</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>230.5124307982049</v>
+        <v>240.9769100970456</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.06910316387904</v>
+        <v>42.26849370565207</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.40091617002009</v>
+        <v>7.914387308078068</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.3546938405404923</v>
+        <v>0.0525884112510252</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-2.812757087057779</v>
+        <v>-1.124186720707706</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1535</v>
+        <v>1516</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>230.1210790292599</v>
+        <v>234.6484352184154</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>50.4</v>
+        <v>18.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>53.75892364839516</v>
+        <v>34.5166154466913</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>28.04293597333676</v>
+        <v>31.548461037437</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5991176397660736</v>
+        <v>0.8302572936319143</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0299976144297632</v>
+        <v>-0.1803676867645468</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1473</v>
+        <v>1519</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>218.7558411721425</v>
+        <v>230.5124307982049</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>20.8</v>
+        <v>773</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>56.68795802934083</v>
+        <v>42.06910316387904</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19.05952255369332</v>
+        <v>13.40091617002009</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.510184268991655</v>
+        <v>0.3546938405404923</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.093228789083421</v>
+        <v>-2.812757087057779</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1522</v>
+        <v>1535</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>214.7805177929433</v>
+        <v>230.1210790292599</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>30.6</v>
+        <v>50.4</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>47.9455706214391</v>
+        <v>53.75892364839516</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.16547225429361</v>
+        <v>28.04293597333676</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7787137621481038</v>
+        <v>0.5991176397660736</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0556177101074788</v>
+        <v>0.0299976144297632</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1218</v>
+        <v>1473</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>210.9512333848652</v>
+        <v>218.7558411721425</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>17.35</v>
+        <v>20.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>28.61767086924057</v>
+        <v>56.68795802934083</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>35.78376056676606</v>
+        <v>19.05952255369332</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.398544295990639</v>
+        <v>1.510184268991655</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0643567367767364</v>
+        <v>0.093228789083421</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1506</v>
+        <v>1522</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>210.757006010509</v>
+        <v>214.7805177929433</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>10.5</v>
+        <v>30.6</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>57.42631881506671</v>
+        <v>47.9455706214391</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>27.40160242923382</v>
+        <v>14.16547225429361</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7893229375856488</v>
+        <v>0.7787137621481038</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.038751946882458</v>
+        <v>-0.0556177101074788</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1541</v>
+        <v>1218</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>210.1035581208789</v>
+        <v>210.9512333848652</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>21.7</v>
+        <v>17.35</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>50.317706144588</v>
+        <v>28.61767086924057</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>10.84208054447334</v>
+        <v>35.78376056676606</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.3240407852332908</v>
+        <v>1.398544295990639</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0317686511425867</v>
+        <v>-0.0643567367767364</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1104</v>
+        <v>1506</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>204.6323515397852</v>
+        <v>210.757006010509</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>27.4</v>
+        <v>10.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>42.95190799525145</v>
+        <v>57.42631881506671</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>30.91367486478174</v>
+        <v>27.40160242923382</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.9372525972714127</v>
+        <v>0.7893229375856488</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.1579432020360567</v>
+        <v>0.038751946882458</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1456</v>
+        <v>1541</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>201.1622864213444</v>
+        <v>210.1035581208789</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>14.1</v>
+        <v>21.7</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>48.39404758207602</v>
+        <v>50.317706144588</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.39027656573642</v>
+        <v>10.84208054447334</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5132876117520482</v>
+        <v>0.3240407852332908</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.1127521716456817</v>
+        <v>0.0317686511425867</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1529</v>
+        <v>1104</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>195.4601473919129</v>
+        <v>204.6323515397852</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>23.1</v>
+        <v>27.4</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>54.97856020521472</v>
+        <v>42.95190799525145</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>12.9280138275367</v>
+        <v>30.91367486478174</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.550093118860412</v>
+        <v>0.9372525972714127</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0136761935917972</v>
+        <v>-0.1579432020360567</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1569</v>
+        <v>1456</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>181.0953237749017</v>
+        <v>201.1622864213444</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>48.6</v>
+        <v>14.1</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>49.11819113162667</v>
+        <v>48.39404758207602</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.45161605330943</v>
+        <v>18.39027656573642</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.8886008932538044</v>
+        <v>0.5132876117520482</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.1716474537486396</v>
+        <v>-0.1127521716456817</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1476</v>
+        <v>1529</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>165.781473523299</v>
+        <v>195.4601473919129</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>323.5</v>
+        <v>23.1</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46.630020193205</v>
+        <v>54.97856020521472</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.87313890116138</v>
+        <v>12.9280138275367</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.5967464446835442</v>
+        <v>1.550093118860412</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.8465030229800012</v>
+        <v>-0.0136761935917972</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1109</v>
+        <v>1569</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>156.1359957350852</v>
+        <v>181.0953237749017</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>14.7</v>
+        <v>48.6</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>52.23637611198459</v>
+        <v>49.11819113162667</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>17.94982536414004</v>
+        <v>17.45161605330943</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.645282458784308</v>
+        <v>0.8886008932538044</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0228803722221669</v>
+        <v>0.1716474537486396</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1325</v>
+        <v>1476</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>151.5486333482552</v>
+        <v>165.781473523299</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>25.35</v>
+        <v>323.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>46.79799020430606</v>
+        <v>46.630020193205</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>23.59969383891433</v>
+        <v>18.87313890116138</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.237967402789372</v>
+        <v>0.5967464446835442</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.0721071029439599</v>
+        <v>-0.8465030229800012</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1439</v>
+        <v>1109</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>148.9802369347259</v>
+        <v>156.1359957350852</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>24.1</v>
+        <v>14.7</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>44.70089854309946</v>
+        <v>52.23637611198459</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>11.28183383142733</v>
+        <v>17.94982536414004</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.9577184016399224</v>
+        <v>1.645282458784308</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0569332263217047</v>
+        <v>0.0228803722221669</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1418</v>
+        <v>1325</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>138.3330244774859</v>
+        <v>151.5486333482552</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>18.45</v>
+        <v>25.35</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>53.52475738733142</v>
+        <v>46.79799020430606</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>14.19883041226118</v>
+        <v>23.59969383891433</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.5843065678594803</v>
+        <v>1.237967402789372</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0034972197100132</v>
+        <v>-0.0721071029439599</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1101</v>
+        <v>1439</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>136.1011030643024</v>
+        <v>148.9802369347259</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>23.65</v>
+        <v>24.1</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>43.68667619378333</v>
+        <v>44.70089854309946</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>13.85330059004084</v>
+        <v>11.28183383142733</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.8317560410123549</v>
+        <v>0.9577184016399224</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,62 +7354,168 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-0.1120393465402794</v>
+        <v>-0.0569332263217047</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>東華</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>138.3330244774859</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>53.52475738733142</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>14.19883041226118</v>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>0.5843065678594803</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N131" s="2" t="n">
+        <v>-0.0034972197100132</v>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>台泥</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>136.1011030643024</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>43.68667619378333</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>13.85330059004084</v>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.8317560410123549</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" s="2" t="n">
+        <v>-0.1120393465402794</v>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
         <v>1530</v>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>亞崴</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D131" s="2" t="n">
+      <c r="C133" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D133" s="2" t="n">
         <v>128.4696454097426</v>
       </c>
-      <c r="E131" s="2" t="n">
+      <c r="E133" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H131" s="2" t="n">
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2" t="n">
         <v>52.32643085740093</v>
       </c>
-      <c r="I131" s="2" t="n">
+      <c r="I133" s="2" t="n">
         <v>18.27140148746092</v>
       </c>
-      <c r="J131" s="2" t="n">
+      <c r="J133" s="2" t="n">
         <v>0.950343234385418</v>
       </c>
-      <c r="K131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N131" s="2" t="n">
+      <c r="K133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" s="2" t="n">
         <v>-0.1864760414469453</v>
       </c>
-      <c r="O131" s="2" t="inlineStr">
+      <c r="O133" s="2" t="inlineStr">
         <is>
           <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
